--- a/generated_reports/CSFA_Report_2026-02-25.xlsx
+++ b/generated_reports/CSFA_Report_2026-02-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance Grid - February" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Attendance - February" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Attendance Grid - February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly Attendance - February" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -76,16 +73,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1856,7 +1853,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 26</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1865,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 26 (2 days)</t>
+          <t>No attendance on date: 23</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1877,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24, 25, 26 (4 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1901,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25, 26 (9 days)</t>
+          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 26</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1925,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25, 26 (16 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25 (15 days)</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1937,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 26</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1949,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25, 26 (9 days)</t>
+          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1961,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24, 25, 26 (4 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>
